--- a/course-design-2/outputs/tables/ch3/11_job_text_semantic_audit.xlsx
+++ b/course-design-2/outputs/tables/ch3/11_job_text_semantic_audit.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_语义事件总体统计" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_语义距离分布" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_完整语义距离分位数" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_显著语义变化候选" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_新增技能统计" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_删除技能统计" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_大模型技能新增统计" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_薪资变化vs完整语义_旧口径" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_职责语义变化" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_要求语义变化" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_技能段语义变化" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_语义变化候选类型" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_人工复核样本" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_完整vs去薪资语义距离" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_去薪资语义距离分位数" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_BGE_Token长度分布" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_BGE_截断统计" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_薪资变化vs去薪资语义" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_非截断样本敏感性" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_语义距离数值检查" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_极端语义变化候选" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="01_语义事件总体统计" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_语义距离分布" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_完整语义距离分位数" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_显著语义变化候选" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="05_新增技能统计" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="06_删除技能统计" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="07_大模型技能新增统计" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="08_薪资变化vs完整语义_旧统计范围" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="09_职责语义变化" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_要求语义变化" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_技能段语义变化" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12_语义变化候选类型" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13_人工复核样本" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="14_完整vs去薪资语义距离" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="15_去薪资语义距离分位数" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="16_BGE_Token长度分布" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="17_BGE_截断统计" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="18_薪资变化vs去薪资语义" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="19_非截断样本敏感性" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="20_语义距离数值检查" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="21_极端语义变化候选" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,7 +543,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>旧口径显著候选数（完整 ≥P90）</t>
+          <t>旧统计范围显著候选数（完整 ≥P90）</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -553,7 +553,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>旧口径极端候选数（完整 ≥P95）</t>
+          <t>旧统计范围极端候选数（完整 ≥P95）</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -573,7 +573,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>因新口径进入显著候选的事件数</t>
+          <t>因新统计范围进入显著候选的事件数</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -583,7 +583,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TF-IDF 词表规模（完整口径）</t>
+          <t>TF-IDF 词表规模（完整文本统计范围）</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -593,7 +593,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TF-IDF 词表规模（去薪资口径）</t>
+          <t>TF-IDF 词表规模（去薪资统计范围）</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -970,42 +970,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>完整口径均值</t>
+          <t>完整文本统计范围均值</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>完整口径中位数</t>
+          <t>完整文本统计范围中位数</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>完整口径P90</t>
+          <t>完整文本统计范围P90</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>完整口径P95</t>
+          <t>完整文本统计范围P95</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>去薪资口径均值</t>
+          <t>去薪资统计范围均值</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>去薪资口径中位数</t>
+          <t>去薪资统计范围中位数</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>去薪资口径P90</t>
+          <t>去薪资统计范围P90</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>去薪资口径P95</t>
+          <t>去薪资统计范围P95</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
+          <t>全体相邻版本语义距离的真实分位数统计</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
+          <t>全体相邻版本语义距离的真实分位数统计</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
+          <t>全体相邻版本语义距离的真实分位数统计</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
+          <t>全体相邻版本语义距离的真实分位数统计</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1260,7 +1260,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>人工复核与业务口径</t>
+          <t>人工复核与业务统计范围</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1281,7 +1281,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>人工复核与业务口径</t>
+          <t>人工复核与业务统计范围</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1298,13 +1298,13 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>先统计真实分布分位数，再结合人工复核样本确认（去薪资口径为正式主判据）</t>
+          <t>先统计真实分布分位数，再结合人工复核样本确认（去薪资统计范围为正式主判据）</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>人工复核与业务口径</t>
+          <t>人工复核与业务统计范围</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1356,7 +1356,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>统计范围</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1418,7 +1418,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>去薪资口径（全样本）</t>
+          <t>去薪资统计范围（全样本）</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1443,14 +1443,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>正式口径：仅描述性关联统计，不做因果推断，不执行统计显著性检验</t>
+          <t>正式统计范围：仅描述性关联统计，不做因果推断，不执行统计显著性检验</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>去薪资口径（全样本）</t>
+          <t>去薪资统计范围（全样本）</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1475,14 +1475,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>正式口径：仅描述性关联统计，不做因果推断，不执行统计显著性检验</t>
+          <t>正式统计范围：仅描述性关联统计，不做因果推断，不执行统计显著性检验</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>去薪资口径（非截断样本）</t>
+          <t>去薪资统计范围（非截断样本）</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1507,14 +1507,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>正式口径：仅描述性关联统计，不做因果推断，不执行统计显著性检验</t>
+          <t>正式统计范围：仅描述性关联统计，不做因果推断，不执行统计显著性检验</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>去薪资口径（非截断样本）</t>
+          <t>去薪资统计范围（非截断样本）</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>正式口径：仅描述性关联统计，不做因果推断，不执行统计显著性检验</t>
+          <t>正式统计范围：仅描述性关联统计，不做因果推断，不执行统计显著性检验</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>样本口径</t>
+          <t>样本统计范围</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>语义口径</t>
+          <t>语义统计范围</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>去薪资口径</t>
+          <t>去薪资统计范围</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>完整口径</t>
+          <t>完整文本统计范围</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>去薪资口径</t>
+          <t>去薪资统计范围</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>完整口径</t>
+          <t>完整文本统计范围</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>去薪资口径</t>
+          <t>去薪资统计范围</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>完整口径</t>
+          <t>完整文本统计范围</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>完整口径版本切换数</t>
+          <t>完整文本统计范围版本切换数</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>去薪资口径版本切换数</t>
+          <t>去薪资统计范围版本切换数</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>是否显著语义变化候选_完整口径</t>
+          <t>是否显著语义变化候选_完整文本统计范围</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
+          <t>全体相邻版本语义距离的真实分位数统计</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
+          <t>全体相邻版本语义距离的真实分位数统计</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
+          <t>全体相邻版本语义距离的真实分位数统计</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
+          <t>全体相邻版本语义距离的真实分位数统计</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>是否显著语义变化候选_完整口径</t>
+          <t>是否显著语义变化候选_完整文本统计范围</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -4447,7 +4447,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>统计范围</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -4509,7 +4509,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>完整口径（旧）</t>
+          <t>完整文本统计范围（旧）</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4534,14 +4534,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>旧口径，仅作回归对照，不作为正式结论</t>
+          <t>旧统计范围，仅作回归对照，不作为正式结论</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>完整口径（旧）</t>
+          <t>完整文本统计范围（旧）</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>旧口径，仅作回归对照，不作为正式结论</t>
+          <t>旧统计范围，仅作回归对照，不作为正式结论</t>
         </is>
       </c>
     </row>

--- a/course-design-2/outputs/tables/ch3/11_job_text_semantic_audit.xlsx
+++ b/course-design-2/outputs/tables/ch3/11_job_text_semantic_audit.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_语义事件总体统计" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_语义距离分布" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_完整语义距离分位数" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_显著语义变化候选" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="05_新增技能统计" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="06_删除技能统计" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="07_大模型技能新增统计" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="08_薪资变化vs完整语义_旧统计范围" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="09_职责语义变化" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_要求语义变化" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11_技能段语义变化" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12_语义变化候选类型" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="13_人工复核样本" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14_完整vs去薪资语义距离" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15_去薪资语义距离分位数" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="16_BGE_Token长度分布" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="17_BGE_截断统计" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="18_薪资变化vs去薪资语义" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="19_非截断样本敏感性" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="20_语义距离数值检查" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="21_极端语义变化候选" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_语义事件总体统计" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_语义距离分布" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_完整语义距离分位数" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_显著语义变化候选" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_新增技能统计" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_删除技能统计" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_大模型技能新增统计" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_薪资变化vs完整语义_旧统计范围" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_职责语义变化" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_要求语义变化" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_技能段语义变化" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_语义变化候选类型" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_人工复核样本" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_完整vs去薪资语义距离" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_去薪资语义距离分位数" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_BGE_Token长度分布" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_BGE_截断统计" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_薪资变化vs去薪资语义" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_非截断样本敏感性" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_语义距离数值检查" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_极端语义变化候选" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,7 +543,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>旧统计范围显著候选数（完整 ≥P90）</t>
+          <t>旧口径显著候选数（完整 ≥P90）</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -553,7 +553,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>旧统计范围极端候选数（完整 ≥P95）</t>
+          <t>旧口径极端候选数（完整 ≥P95）</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -573,7 +573,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>因新统计范围进入显著候选的事件数</t>
+          <t>因新口径进入显著候选的事件数</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -583,7 +583,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TF-IDF 词表规模（完整文本统计范围）</t>
+          <t>TF-IDF 词表规模（完整口径）</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -593,7 +593,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TF-IDF 词表规模（去薪资统计范围）</t>
+          <t>TF-IDF 词表规模（去薪资口径）</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -726,7 +726,6 @@
           <t>任职要求语义距离均值</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -734,7 +733,6 @@
           <t>任职要求语义距离中位数</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -742,7 +740,6 @@
           <t>任职要求语义距离P90</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -750,7 +747,6 @@
           <t>任职要求语义距离最大值</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -804,7 +800,6 @@
           <t>技能段语义距离均值</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -812,7 +807,6 @@
           <t>技能段语义距离中位数</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -820,7 +814,6 @@
           <t>技能段语义距离P90</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -828,7 +821,6 @@
           <t>技能段语义距离最大值</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -943,7 +935,9 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1"/>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1048,19 +1042,6 @@
       <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Embedding 距离不是可加性分解，该差值仅作诊断，禁止解释为「薪资文本贡献率」</t>
@@ -1076,19 +1057,6 @@
       <c r="B3" t="n">
         <v>0</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Embedding 距离不是可加性分解，该差值仅作诊断，禁止解释为「薪资文本贡献率」</t>
@@ -1104,19 +1072,6 @@
       <c r="B4" t="n">
         <v>0</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Embedding 距离不是可加性分解，该差值仅作诊断，禁止解释为「薪资文本贡献率」</t>
@@ -1170,13 +1125,12 @@
           <t>岗位描述语义距离_去薪资P50</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计</t>
+          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1191,13 +1145,12 @@
           <t>岗位描述语义距离_去薪资P75</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计</t>
+          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1212,13 +1165,12 @@
           <t>岗位描述语义距离_去薪资P90</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计</t>
+          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1233,13 +1185,12 @@
           <t>岗位描述语义距离_去薪资P95</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计</t>
+          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1257,10 +1208,9 @@
       <c r="B6" t="n">
         <v>0.9</v>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>人工复核与业务统计范围</t>
+          <t>人工复核与业务口径</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1278,10 +1228,9 @@
       <c r="B7" t="n">
         <v>0.95</v>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>人工复核与业务统计范围</t>
+          <t>人工复核与业务口径</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1298,13 +1247,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>先统计真实分布分位数，再结合人工复核样本确认（去薪资统计范围为正式主判据）</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>先统计真实分布分位数，再结合人工复核样本确认（去薪资口径为正式主判据）</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>人工复核与业务统计范围</t>
+          <t>人工复核与业务口径</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1326,7 +1274,9 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1"/>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1339,7 +1289,9 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1"/>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1418,7 +1370,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>去薪资统计范围（全样本）</t>
+          <t>去薪资口径（全样本）</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1429,12 +1381,6 @@
       <c r="C2" t="n">
         <v>47</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
         <v>0</v>
       </c>
@@ -1443,14 +1389,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>正式统计范围：仅描述性关联统计，不做因果推断，不执行统计显著性检验</t>
+          <t>正式口径：仅描述性关联统计，不做因果推断，不执行统计显著性检验</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>去薪资统计范围（全样本）</t>
+          <t>去薪资口径（全样本）</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1461,12 +1407,6 @@
       <c r="C3" t="n">
         <v>393</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
         <v>0</v>
       </c>
@@ -1475,14 +1415,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>正式统计范围：仅描述性关联统计，不做因果推断，不执行统计显著性检验</t>
+          <t>正式口径：仅描述性关联统计，不做因果推断，不执行统计显著性检验</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>去薪资统计范围（非截断样本）</t>
+          <t>去薪资口径（非截断样本）</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1493,12 +1433,6 @@
       <c r="C4" t="n">
         <v>47</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>0</v>
       </c>
@@ -1507,14 +1441,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>正式统计范围：仅描述性关联统计，不做因果推断，不执行统计显著性检验</t>
+          <t>正式口径：仅描述性关联统计，不做因果推断，不执行统计显著性检验</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>去薪资统计范围（非截断样本）</t>
+          <t>去薪资口径（非截断样本）</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1525,12 +1459,6 @@
       <c r="C5" t="n">
         <v>393</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>0</v>
       </c>
@@ -1539,7 +1467,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>正式统计范围：仅描述性关联统计，不做因果推断，不执行统计显著性检验</t>
+          <t>正式口径：仅描述性关联统计，不做因果推断，不执行统计显著性检验</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1545,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>去薪资统计范围</t>
+          <t>去薪资口径</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1626,10 +1554,6 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -1647,7 +1571,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>完整文本统计范围</t>
+          <t>完整口径</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1656,10 +1580,6 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1677,7 +1597,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>去薪资统计范围</t>
+          <t>去薪资口径</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1686,10 +1606,6 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1707,7 +1623,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>完整文本统计范围</t>
+          <t>完整口径</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1716,10 +1632,6 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1737,7 +1649,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>去薪资统计范围</t>
+          <t>去薪资口径</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1746,10 +1658,6 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1767,7 +1675,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>完整文本统计范围</t>
+          <t>完整口径</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1776,10 +1684,6 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -2484,13 +2388,12 @@
           <t>岗位描述语义距离_完整P50</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计</t>
+          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2505,13 +2408,12 @@
           <t>岗位描述语义距离_完整P75</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计</t>
+          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2526,13 +2428,12 @@
           <t>岗位描述语义距离_完整P90</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计</t>
+          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2547,13 +2448,12 @@
           <t>岗位描述语义距离_完整P95</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>全体相邻版本语义距离的真实分位数统计</t>
+          <t>全体相邻版本语义距离的真实分位数统计（非人工拍脑袋设定）</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4509,7 +4409,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>完整文本统计范围（旧）</t>
+          <t>完整口径（旧）</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4520,12 +4420,6 @@
       <c r="C2" t="n">
         <v>47</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
         <v>0</v>
       </c>
@@ -4534,14 +4428,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>旧统计范围，仅作回归对照，不作为正式结论</t>
+          <t>旧口径，仅作回归对照，不作为正式结论</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>完整文本统计范围（旧）</t>
+          <t>完整口径（旧）</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4552,12 +4446,6 @@
       <c r="C3" t="n">
         <v>393</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
         <v>0</v>
       </c>
@@ -4566,7 +4454,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>旧统计范围，仅作回归对照，不作为正式结论</t>
+          <t>旧口径，仅作回归对照，不作为正式结论</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4510,6 @@
           <t>职责语义距离均值</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4630,7 +4517,6 @@
           <t>职责语义距离中位数</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4638,7 +4524,6 @@
           <t>职责语义距离P90</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4646,7 +4531,6 @@
           <t>职责语义距离最大值</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
